--- a/artifacts/tables/model-analysis.xlsx
+++ b/artifacts/tables/model-analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jn\dev\llm-ensemble\artifacts\analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\donista\dev\llm-ensemble\artifacts\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B54C51E-CA44-4119-AE6D-BA82BBA6362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D736C2-543B-47DC-BD9B-FF9D4DF92446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
   </bookViews>
   <sheets>
     <sheet name="model-analysis" sheetId="6" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="196">
   <si>
     <t>model_id</t>
   </si>
@@ -666,7 +666,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -701,8 +701,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +731,12 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -734,13 +747,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -769,8 +783,10 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
@@ -971,7 +987,7 @@
     <tableColumn id="13" xr3:uid="{0516A28C-43F7-4683-AB8C-D7BCE4C57A35}" name="other links" dataDxfId="23" dataCellStyle="Normal"/>
     <tableColumn id="6" xr3:uid="{A32E4A17-CBEB-4B4E-82ED-3C03A0E0104C}" name="note" dataDxfId="22" dataCellStyle="Normal"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1325,26 +1341,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADB490E-EB07-4EE4-BECE-4EE10CDDA4E5}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultRowHeight="40" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.1796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="46.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="77.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.26953125" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7265625" style="1"/>
+    <col min="7" max="7" width="19.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="46.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="77.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>163</v>
       </c>
@@ -1391,7 +1407,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1429,7 +1445,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1467,7 +1483,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1496,7 +1512,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1539,87 +1555,93 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="8">
         <v>6.3500000000000001E-2</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="9">
         <v>45950.107581018514</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="8" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="10">
         <v>0.02</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <v>45560</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8" t="s">
+      <c r="K7" s="10"/>
+      <c r="L7" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="10" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1657,7 +1679,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -1704,7 +1726,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1733,7 +1755,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1774,7 +1796,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1803,7 +1825,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1835,7 +1857,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>30</v>
       </c>
@@ -1880,7 +1902,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>140</v>
       </c>
@@ -1925,7 +1947,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
@@ -1984,31 +2006,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030068A6-33CF-4092-B5E5-65A22CC450D3}">
   <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultRowHeight="40" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="125.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="66.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="46.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="77.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="68.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="110.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="49.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="125.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="77.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="68.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="110.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="49.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.7265625" style="1"/>
+    <col min="21" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2070,7 +2092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2132,7 +2154,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2194,7 +2216,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2256,7 +2278,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -2318,7 +2340,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
@@ -2380,7 +2402,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -2442,7 +2464,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2504,7 +2526,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -2566,7 +2588,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -2628,7 +2650,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -2690,7 +2712,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -2752,7 +2774,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2814,7 +2836,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -2876,7 +2898,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -2938,7 +2960,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -3000,8 +3022,8 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -3016,7 +3038,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -3031,7 +3053,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -3046,7 +3068,7 @@
       <c r="L25"/>
       <c r="M25"/>
     </row>
-    <row r="26" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>

--- a/artifacts/tables/model-analysis.xlsx
+++ b/artifacts/tables/model-analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\donista\dev\llm-ensemble\artifacts\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D736C2-543B-47DC-BD9B-FF9D4DF92446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F256618-21CC-4BA0-B050-4E18C6C05EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
   </bookViews>
@@ -733,7 +733,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -754,7 +754,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -783,10 +783,16 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
+    <cellStyle name="40% - Accent5" xfId="4" builtinId="47"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
@@ -968,7 +974,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2515506D-7B69-4B06-9BF5-773B122E6626}" name="Table6" displayName="Table6" ref="A1:O16" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A1:O16" xr:uid="{2515506D-7B69-4B06-9BF5-773B122E6626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O16">
-    <sortCondition ref="A1:A16"/>
+    <sortCondition ref="D1:D16"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{D58B9424-3D3A-43E3-A095-F707C822ADC7}" name="Model" dataDxfId="36" dataCellStyle="Normal"/>
@@ -1355,9 +1361,10 @@
     <col min="10" max="10" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="46.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="77.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.28515625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7109375" style="1"/>
+    <col min="13" max="13" width="51" style="1" customWidth="1"/>
+    <col min="14" max="14" width="55.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="27.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1408,392 +1415,395 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="G2" s="4">
-        <v>45860.725185185191</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>121</v>
+      <c r="A2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="8">
+        <v>6.3500000000000001E-2</v>
+      </c>
+      <c r="G2" s="9">
+        <v>45950.107581018514</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="1">
-        <v>9.375E-2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>45640.274907407409</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="A3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="G3" s="10">
+        <v>45560</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="K3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>142</v>
+      <c r="J3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F4" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G4" s="4">
-        <v>45806.714618055557</v>
-      </c>
-      <c r="K4" s="1" t="b">
-        <v>1</v>
+        <v>45582</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F5" s="3">
-        <v>4.2591860000000002E-2</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="5">
-        <v>45729.943402777775</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>45993.555092592593</v>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>123</v>
-      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4.2591860000000002E-2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>45729.943402777775</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3" t="s">
+      <c r="N6" s="3"/>
+      <c r="O6" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D7" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="8">
-        <v>6.3500000000000001E-2</v>
-      </c>
-      <c r="G6" s="9">
-        <v>45950.107581018514</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="F7" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>45724.049583333333</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="G7" s="10">
-        <v>45560</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="K7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="G8" s="12">
+        <v>45860.725185185191</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="1">
+        <v>9.375E-2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>45640.274907407409</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="G8" s="4">
-        <v>45700.959699074076</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9" s="3">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G9" s="5">
-        <v>45724.049583333333</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K9" s="3" t="b">
+      <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>153</v>
+      <c r="L9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>45806.714618055557</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>0.04</v>
       </c>
-      <c r="G10" s="4">
-        <v>45582</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="G11" s="5">
-        <v>45993.555092592593</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>154</v>
+      <c r="G11" s="4">
+        <v>45700.959699074076</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1858,53 +1868,53 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="9">
-        <v>45905.884340277778</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
+      <c r="A14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" s="6">
+        <v>8.6499999999999994E-2</v>
+      </c>
+      <c r="G14" s="7">
+        <v>45775.905462962968</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K14" s="8" t="b">
+      <c r="K14" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="L14" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>151</v>
+      <c r="L14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>139</v>
@@ -1916,19 +1926,19 @@
         <v>193</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F15" s="6">
-        <v>8.6499999999999994E-2</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G15" s="7">
-        <v>45775.905462962968</v>
+        <v>45944.732731481483</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>179</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>123</v>
@@ -1937,61 +1947,61 @@
         <v>1</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="N15" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="O15" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="A16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F16" s="6">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="G16" s="7">
-        <v>45944.732731481483</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J16" s="6" t="s">
+      <c r="F16" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="9">
+        <v>45905.884340277778</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="K16" s="6" t="b">
+      <c r="J16" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K16" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>150</v>
+      <c r="L16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/tables/model-analysis.xlsx
+++ b/artifacts/tables/model-analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\donista\dev\llm-ensemble\artifacts\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F256618-21CC-4BA0-B050-4E18C6C05EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED849D6-377D-4DB6-9CEB-ABB189EA558E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="196">
   <si>
     <t>model_id</t>
   </si>
@@ -733,7 +733,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -792,7 +792,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="40% - Accent5" xfId="4" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
@@ -1661,83 +1661,88 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="3">
         <v>0.15</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="5">
         <v>45860.725185185191</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="O8" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="11">
         <v>9.375E-2</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="12">
         <v>45640.274907407409</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="K9" s="1" t="b">
+      <c r="J9" s="11"/>
+      <c r="K9" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="11" t="s">
         <v>142</v>
       </c>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
     </row>
     <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">

--- a/artifacts/tables/model-analysis.xlsx
+++ b/artifacts/tables/model-analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\donista\dev\llm-ensemble\artifacts\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jn\dev\llm-ensemble\artifacts\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED849D6-377D-4DB6-9CEB-ABB189EA558E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4E2DE7-E1A9-4CF1-BD07-8A7F31A4E5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
   </bookViews>
   <sheets>
     <sheet name="model-analysis" sheetId="6" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="197">
   <si>
     <t>model_id</t>
   </si>
@@ -443,9 +443,6 @@
     <t>Text</t>
   </si>
   <si>
-    <t>efficient, low-latency inference, suitable for edge and mobile deployments</t>
-  </si>
-  <si>
     <t>https://openrouter.ai/mistralai/ministral-3b-2512</t>
   </si>
   <si>
@@ -485,9 +482,6 @@
     <t>content safety classification</t>
   </si>
   <si>
-    <t>reasoning-heavy tasks and efficient dialogue, creative writing, role-playing, multi-turn dialogues</t>
-  </si>
-  <si>
     <t>Alibaba</t>
   </si>
   <si>
@@ -614,30 +608,18 @@
     <t>text generation, chatbots, summarization, image data extraction, NLP, knowledge exploration</t>
   </si>
   <si>
-    <t>multilingual dialogue, agentic retrieval and summarization</t>
-  </si>
-  <si>
     <t>image captioning, classification, real-time translation, data extraction, content generation</t>
   </si>
   <si>
     <t>fast, memory-efficient inference</t>
   </si>
   <si>
-    <t xml:space="preserve">general purpose reasoning, code and chat model </t>
-  </si>
-  <si>
     <t>GUI environments, desktop interfaces, web browsers, mobile systems, games</t>
   </si>
   <si>
     <t>GUI screenshots, interaction traces, tutorials, synthetic data</t>
   </si>
   <si>
-    <t>image/document description, translation, content generation</t>
-  </si>
-  <si>
-    <t>on-device and edge computing, orchestrating agents, memory/compute/latency constrained environments</t>
-  </si>
-  <si>
     <t>high throughput, latency-sensitive chatbots, code assistants, RAG, tool use</t>
   </si>
   <si>
@@ -657,6 +639,27 @@
   </si>
   <si>
     <t>9B</t>
+  </si>
+  <si>
+    <t>medium fast</t>
+  </si>
+  <si>
+    <t>multilingual dialogue, agentic retrieval, summarization</t>
+  </si>
+  <si>
+    <t>on-device and edge computing, orchestrating agents, resource-constrained environments</t>
+  </si>
+  <si>
+    <t>general purpose reasoning, code, chat</t>
+  </si>
+  <si>
+    <t>image and document description, translation, content generation</t>
+  </si>
+  <si>
+    <t>low-latency, edge and mobile deployments</t>
+  </si>
+  <si>
+    <t>reasoning-heavy tasks, efficient dialogue, creative writing, role-playing, dialogues</t>
   </si>
 </sst>
 </file>
@@ -733,7 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -754,7 +757,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -790,9 +793,12 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
+    <cellStyle name="40% - Accent2" xfId="4" builtinId="35"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
@@ -800,6 +806,18 @@
   </cellStyles>
   <dxfs count="39">
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -868,12 +886,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -974,7 +986,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2515506D-7B69-4B06-9BF5-773B122E6626}" name="Table6" displayName="Table6" ref="A1:O16" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <autoFilter ref="A1:O16" xr:uid="{2515506D-7B69-4B06-9BF5-773B122E6626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O16">
-    <sortCondition ref="D1:D16"/>
+    <sortCondition ref="D2:D16"/>
+    <sortCondition ref="A2:A16"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{D58B9424-3D3A-43E3-A095-F707C822ADC7}" name="Model" dataDxfId="36" dataCellStyle="Normal"/>
@@ -984,46 +997,46 @@
     <tableColumn id="10" xr3:uid="{E2191CB7-B6FF-404B-9962-2076D050CEB7}" name="Ctx" dataDxfId="32" dataCellStyle="Normal"/>
     <tableColumn id="11" xr3:uid="{521CF197-E079-4F72-80B5-C09DE2953B51}" name="Cost" dataDxfId="31" dataCellStyle="Normal"/>
     <tableColumn id="14" xr3:uid="{A8A63267-BB5B-463C-8484-6D28406DE281}" name="release" dataDxfId="30" dataCellStyle="Neutral"/>
-    <tableColumn id="3" xr3:uid="{FB0B91F9-CC4A-4F2F-B7FA-8F4849679D55}" name="Training Data" dataDxfId="29" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{710908A7-2136-47EA-9EA4-61FB50EB1236}" name="Input" dataDxfId="28" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{E231CFF8-225F-4DDB-B084-555A9DCA2D9B}" name="Output modalities" dataDxfId="27" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{ACE0B5AB-F0DE-44AF-BDA1-3D7933AA8AF9}" name="Reasoning" dataDxfId="26" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{81A13497-D9E5-4952-BA69-5ECB2716882B}" name="Use Case" dataDxfId="25" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{2143AF97-E365-40D2-8B0E-2F9755C0F893}" name="openrouter link" dataDxfId="24" dataCellStyle="Normal"/>
-    <tableColumn id="13" xr3:uid="{0516A28C-43F7-4683-AB8C-D7BCE4C57A35}" name="other links" dataDxfId="23" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{A32E4A17-CBEB-4B4E-82ED-3C03A0E0104C}" name="note" dataDxfId="22" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{FB0B91F9-CC4A-4F2F-B7FA-8F4849679D55}" name="Use Case" dataDxfId="1" dataCellStyle="Neutral"/>
+    <tableColumn id="4" xr3:uid="{710908A7-2136-47EA-9EA4-61FB50EB1236}" name="Input" dataDxfId="29" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{E231CFF8-225F-4DDB-B084-555A9DCA2D9B}" name="Output modalities" dataDxfId="28" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{ACE0B5AB-F0DE-44AF-BDA1-3D7933AA8AF9}" name="Reasoning" dataDxfId="27" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{81A13497-D9E5-4952-BA69-5ECB2716882B}" name="Training Data" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{2143AF97-E365-40D2-8B0E-2F9755C0F893}" name="openrouter link" dataDxfId="26" dataCellStyle="Normal"/>
+    <tableColumn id="13" xr3:uid="{0516A28C-43F7-4683-AB8C-D7BCE4C57A35}" name="other links" dataDxfId="25" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{A32E4A17-CBEB-4B4E-82ED-3C03A0E0104C}" name="note" dataDxfId="24" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E74BC6F4-E459-4841-A57F-F7392AD4352B}" name="models_202601091237" displayName="models_202601091237" ref="A1:T16" tableType="queryTable" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E74BC6F4-E459-4841-A57F-F7392AD4352B}" name="models_202601091237" displayName="models_202601091237" ref="A1:T16" tableType="queryTable" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A1:T16" xr:uid="{E74BC6F4-E459-4841-A57F-F7392AD4352B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T16">
     <sortCondition ref="A1:A16"/>
   </sortState>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{78D3B969-8519-472B-B7DC-40B2AB389EDF}" uniqueName="1" name="model_id" queryTableFieldId="1" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{2775870E-97E4-4A13-8631-08858414ABE9}" uniqueName="2" name="canonical_slug" queryTableFieldId="2" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{9123C448-65CD-42A3-A8DF-FA33362CF2EB}" uniqueName="3" name="model_name" queryTableFieldId="3" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{23ACEE67-B62B-4941-8C62-48ACD4FFD384}" uniqueName="4" name="description" queryTableFieldId="4" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{EBBFCEC0-7D31-4CAD-A2DD-E444E8C840AD}" uniqueName="5" name="created" queryTableFieldId="5" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{235BBD11-52A4-432B-B259-1FEF7849A476}" uniqueName="6" name="prompt_cost_per_1m" queryTableFieldId="6" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{C125A326-71DC-498F-9CF6-9D4261986ABF}" uniqueName="7" name="completion_cost_per_1m" queryTableFieldId="7" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{C48D515D-EA76-4B8D-9D9B-3F86005C986D}" uniqueName="8" name="avg_cost_per_1m" queryTableFieldId="8" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{0C9AC00E-B68D-4AF7-9758-7543FA934B04}" uniqueName="9" name="request_cost" queryTableFieldId="9" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{CED2343B-816C-4F54-B994-E7FC118F7157}" uniqueName="10" name="image_cost" queryTableFieldId="10" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{6D67746F-12ED-4C55-AF34-2427D5CEA21F}" uniqueName="11" name="is_free" queryTableFieldId="11" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{D41C5152-EBB5-4D0D-A3D0-E2AF2584030A}" uniqueName="12" name="param_size" queryTableFieldId="12" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{3F7A75A1-5B17-4021-B0DF-2D6D58413453}" uniqueName="13" name="context_length" queryTableFieldId="13" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{77302B12-EFD5-4388-8BAA-BE5B0C3E0D4D}" uniqueName="14" name="architecture" queryTableFieldId="14" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{A4F53FD9-655C-485A-AF2A-687B004D91BB}" uniqueName="15" name="top_provider" queryTableFieldId="15" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{8DC3E8E9-B9CD-4A00-ABDC-CAEB3EF2F82E}" uniqueName="16" name="per_request_limits" queryTableFieldId="16" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{89C9A0EC-EEDE-4BF2-9AD6-BFB8C497DC96}" uniqueName="17" name="supported_parameters" queryTableFieldId="17" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{782F3ED8-5B9C-4F0A-9BF7-C9083C418B46}" uniqueName="18" name="default_parameters" queryTableFieldId="18" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{B52B03E2-D483-4B78-B500-90C21984E5CF}" uniqueName="19" name="last_updated" queryTableFieldId="19" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{A9E6322E-6414-4705-8C48-2E513F4761A1}" uniqueName="20" name="created_at" queryTableFieldId="20" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{78D3B969-8519-472B-B7DC-40B2AB389EDF}" uniqueName="1" name="model_id" queryTableFieldId="1" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{2775870E-97E4-4A13-8631-08858414ABE9}" uniqueName="2" name="canonical_slug" queryTableFieldId="2" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{9123C448-65CD-42A3-A8DF-FA33362CF2EB}" uniqueName="3" name="model_name" queryTableFieldId="3" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{23ACEE67-B62B-4941-8C62-48ACD4FFD384}" uniqueName="4" name="description" queryTableFieldId="4" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{EBBFCEC0-7D31-4CAD-A2DD-E444E8C840AD}" uniqueName="5" name="created" queryTableFieldId="5" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{235BBD11-52A4-432B-B259-1FEF7849A476}" uniqueName="6" name="prompt_cost_per_1m" queryTableFieldId="6" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{C125A326-71DC-498F-9CF6-9D4261986ABF}" uniqueName="7" name="completion_cost_per_1m" queryTableFieldId="7" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{C48D515D-EA76-4B8D-9D9B-3F86005C986D}" uniqueName="8" name="avg_cost_per_1m" queryTableFieldId="8" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{0C9AC00E-B68D-4AF7-9758-7543FA934B04}" uniqueName="9" name="request_cost" queryTableFieldId="9" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{CED2343B-816C-4F54-B994-E7FC118F7157}" uniqueName="10" name="image_cost" queryTableFieldId="10" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{6D67746F-12ED-4C55-AF34-2427D5CEA21F}" uniqueName="11" name="is_free" queryTableFieldId="11" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{D41C5152-EBB5-4D0D-A3D0-E2AF2584030A}" uniqueName="12" name="param_size" queryTableFieldId="12" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{3F7A75A1-5B17-4021-B0DF-2D6D58413453}" uniqueName="13" name="context_length" queryTableFieldId="13" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{77302B12-EFD5-4388-8BAA-BE5B0C3E0D4D}" uniqueName="14" name="architecture" queryTableFieldId="14" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{A4F53FD9-655C-485A-AF2A-687B004D91BB}" uniqueName="15" name="top_provider" queryTableFieldId="15" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{8DC3E8E9-B9CD-4A00-ABDC-CAEB3EF2F82E}" uniqueName="16" name="per_request_limits" queryTableFieldId="16" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{89C9A0EC-EEDE-4BF2-9AD6-BFB8C497DC96}" uniqueName="17" name="supported_parameters" queryTableFieldId="17" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{782F3ED8-5B9C-4F0A-9BF7-C9083C418B46}" uniqueName="18" name="default_parameters" queryTableFieldId="18" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{B52B03E2-D483-4B78-B500-90C21984E5CF}" uniqueName="19" name="last_updated" queryTableFieldId="19" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{A9E6322E-6414-4705-8C48-2E513F4761A1}" uniqueName="20" name="created_at" queryTableFieldId="20" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1347,53 +1360,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADB490E-EB07-4EE4-BECE-4EE10CDDA4E5}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="40" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="46.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="49.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="51" style="1" customWidth="1"/>
-    <col min="14" max="14" width="55.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="27.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.7109375" style="1"/>
+    <col min="14" max="14" width="55.1796875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="27.54296875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
@@ -1401,8 +1414,8 @@
       <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>132</v>
+      <c r="L1" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>113</v>
@@ -1411,10 +1424,10 @@
         <v>122</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>46</v>
       </c>
@@ -1425,10 +1438,10 @@
         <v>119</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2" s="8">
         <v>6.3500000000000001E-2</v>
@@ -1437,7 +1450,7 @@
         <v>45950.107581018514</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>123</v>
@@ -1445,17 +1458,17 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N2" s="8"/>
       <c r="O2" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>20</v>
       </c>
@@ -1466,10 +1479,10 @@
         <v>119</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F3" s="10">
         <v>0.02</v>
@@ -1478,7 +1491,7 @@
         <v>45560</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>123</v>
@@ -1488,7 +1501,7 @@
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>114</v>
@@ -1497,39 +1510,45 @@
         <v>115</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="G4" s="12">
+        <v>45582</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="G4" s="4">
-        <v>45582</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1537,13 +1556,13 @@
         <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F5" s="3">
         <v>0.1</v>
@@ -1551,26 +1570,26 @@
       <c r="G5" s="5">
         <v>45993.555092592593</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="I5" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -1581,10 +1600,10 @@
         <v>119</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F6" s="3">
         <v>4.2591860000000002E-2</v>
@@ -1593,27 +1612,27 @@
         <v>45729.943402777775</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>123</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
@@ -1624,10 +1643,10 @@
         <v>119</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F7" s="3">
         <v>7.4999999999999997E-2</v>
@@ -1636,10 +1655,10 @@
         <v>45724.049583333333</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>123</v>
@@ -1648,19 +1667,19 @@
         <v>1</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1668,13 +1687,13 @@
         <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F8" s="3">
         <v>0.15</v>
@@ -1682,16 +1701,16 @@
       <c r="G8" s="5">
         <v>45860.725185185191</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>186</v>
+      <c r="H8" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>120</v>
@@ -1700,51 +1719,53 @@
         <v>121</v>
       </c>
       <c r="O8" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="3">
+        <v>9.375E-2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>45640.274907407409</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F9" s="11">
-        <v>9.375E-2</v>
-      </c>
-      <c r="G9" s="12">
-        <v>45640.274907407409</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-    </row>
-    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -1752,13 +1773,13 @@
         <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F10" s="1">
         <v>7.4999999999999997E-2</v>
@@ -1766,14 +1787,18 @@
       <c r="G10" s="4">
         <v>45806.714618055557</v>
       </c>
+      <c r="I10" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L10" s="13"/>
       <c r="M10" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1784,10 +1809,10 @@
         <v>119</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F11" s="1">
         <v>0.04</v>
@@ -1796,7 +1821,7 @@
         <v>45700.959699074076</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>123</v>
@@ -1804,43 +1829,49 @@
       <c r="J11" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>137</v>
+      <c r="L11" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="C12" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" s="11">
         <v>0.1</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="12">
         <v>45582</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -1848,13 +1879,13 @@
         <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F13" s="1">
         <v>0.15</v>
@@ -1862,31 +1893,32 @@
       <c r="G13" s="4">
         <v>45993.556180555555</v>
       </c>
+      <c r="H13" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="I13" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="L13" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F14" s="6">
         <v>8.6499999999999994E-2</v>
@@ -1895,7 +1927,7 @@
         <v>45775.905462962968</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>123</v>
@@ -1907,31 +1939,31 @@
         <v>1</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N14" s="6"/>
       <c r="O14" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F15" s="6">
         <v>0.28999999999999998</v>
@@ -1940,10 +1972,10 @@
         <v>45944.732731481483</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>123</v>
@@ -1952,19 +1984,19 @@
         <v>1</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="M15" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>131</v>
-      </c>
       <c r="O15" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>30</v>
       </c>
@@ -1975,10 +2007,10 @@
         <v>119</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F16" s="8">
         <v>0.1</v>
@@ -1986,7 +2018,9 @@
       <c r="G16" s="9">
         <v>45905.884340277778</v>
       </c>
-      <c r="H16" s="8"/>
+      <c r="H16" s="8" t="s">
+        <v>193</v>
+      </c>
       <c r="I16" s="8" t="s">
         <v>123</v>
       </c>
@@ -1996,17 +2030,15 @@
       <c r="K16" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="8" t="s">
-        <v>184</v>
-      </c>
+      <c r="L16" s="8"/>
       <c r="M16" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2021,31 +2053,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030068A6-33CF-4092-B5E5-65A22CC450D3}">
   <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="40" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="125.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="66.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="46.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="77.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="68.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="110.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="49.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="125.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="77.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="68.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="110.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="49.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.7109375" style="1"/>
+    <col min="21" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2107,7 +2139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2169,7 +2201,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2231,7 +2263,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2293,7 +2325,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -2355,7 +2387,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
@@ -2417,7 +2449,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -2479,7 +2511,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2541,7 +2573,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -2603,7 +2635,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -2665,7 +2697,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -2727,7 +2759,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -2789,7 +2821,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2851,7 +2883,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -2913,7 +2945,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,7 +3007,7 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -3037,8 +3069,8 @@
         <v>46031.317484479165</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -3053,7 +3085,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -3068,7 +3100,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -3083,7 +3115,7 @@
       <c r="L25"/>
       <c r="M25"/>
     </row>
-    <row r="26" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>

--- a/artifacts/tables/model-analysis.xlsx
+++ b/artifacts/tables/model-analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jn\dev\llm-ensemble\artifacts\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4E2DE7-E1A9-4CF1-BD07-8A7F31A4E5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF1B7F5-8C71-43B7-A2D3-19626EF5B045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="198">
   <si>
     <t>model_id</t>
   </si>
@@ -660,6 +660,9 @@
   </si>
   <si>
     <t>reasoning-heavy tasks, efficient dialogue, creative writing, role-playing, dialogues</t>
+  </si>
+  <si>
+    <t>overlap with other model</t>
   </si>
 </sst>
 </file>
@@ -757,7 +760,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -793,9 +796,6 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="40% - Accent2" xfId="4" builtinId="35"/>
@@ -806,98 +806,98 @@
   </cellStyles>
   <dxfs count="39">
     <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -997,46 +997,46 @@
     <tableColumn id="10" xr3:uid="{E2191CB7-B6FF-404B-9962-2076D050CEB7}" name="Ctx" dataDxfId="32" dataCellStyle="Normal"/>
     <tableColumn id="11" xr3:uid="{521CF197-E079-4F72-80B5-C09DE2953B51}" name="Cost" dataDxfId="31" dataCellStyle="Normal"/>
     <tableColumn id="14" xr3:uid="{A8A63267-BB5B-463C-8484-6D28406DE281}" name="release" dataDxfId="30" dataCellStyle="Neutral"/>
-    <tableColumn id="3" xr3:uid="{FB0B91F9-CC4A-4F2F-B7FA-8F4849679D55}" name="Use Case" dataDxfId="1" dataCellStyle="Neutral"/>
-    <tableColumn id="4" xr3:uid="{710908A7-2136-47EA-9EA4-61FB50EB1236}" name="Input" dataDxfId="29" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{E231CFF8-225F-4DDB-B084-555A9DCA2D9B}" name="Output modalities" dataDxfId="28" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{ACE0B5AB-F0DE-44AF-BDA1-3D7933AA8AF9}" name="Reasoning" dataDxfId="27" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{81A13497-D9E5-4952-BA69-5ECB2716882B}" name="Training Data" dataDxfId="0" dataCellStyle="Normal"/>
-    <tableColumn id="12" xr3:uid="{2143AF97-E365-40D2-8B0E-2F9755C0F893}" name="openrouter link" dataDxfId="26" dataCellStyle="Normal"/>
-    <tableColumn id="13" xr3:uid="{0516A28C-43F7-4683-AB8C-D7BCE4C57A35}" name="other links" dataDxfId="25" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{A32E4A17-CBEB-4B4E-82ED-3C03A0E0104C}" name="note" dataDxfId="24" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{FB0B91F9-CC4A-4F2F-B7FA-8F4849679D55}" name="Use Case" dataDxfId="29" dataCellStyle="Neutral"/>
+    <tableColumn id="4" xr3:uid="{710908A7-2136-47EA-9EA4-61FB50EB1236}" name="Input" dataDxfId="28" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{E231CFF8-225F-4DDB-B084-555A9DCA2D9B}" name="Output modalities" dataDxfId="27" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{ACE0B5AB-F0DE-44AF-BDA1-3D7933AA8AF9}" name="Reasoning" dataDxfId="26" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{81A13497-D9E5-4952-BA69-5ECB2716882B}" name="Training Data" dataDxfId="25" dataCellStyle="Normal"/>
+    <tableColumn id="12" xr3:uid="{2143AF97-E365-40D2-8B0E-2F9755C0F893}" name="openrouter link" dataDxfId="24" dataCellStyle="Normal"/>
+    <tableColumn id="13" xr3:uid="{0516A28C-43F7-4683-AB8C-D7BCE4C57A35}" name="other links" dataDxfId="23" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{A32E4A17-CBEB-4B4E-82ED-3C03A0E0104C}" name="note" dataDxfId="22" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E74BC6F4-E459-4841-A57F-F7392AD4352B}" name="models_202601091237" displayName="models_202601091237" ref="A1:T16" tableType="queryTable" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E74BC6F4-E459-4841-A57F-F7392AD4352B}" name="models_202601091237" displayName="models_202601091237" ref="A1:T16" tableType="queryTable" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:T16" xr:uid="{E74BC6F4-E459-4841-A57F-F7392AD4352B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T16">
     <sortCondition ref="A1:A16"/>
   </sortState>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{78D3B969-8519-472B-B7DC-40B2AB389EDF}" uniqueName="1" name="model_id" queryTableFieldId="1" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{2775870E-97E4-4A13-8631-08858414ABE9}" uniqueName="2" name="canonical_slug" queryTableFieldId="2" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{9123C448-65CD-42A3-A8DF-FA33362CF2EB}" uniqueName="3" name="model_name" queryTableFieldId="3" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{23ACEE67-B62B-4941-8C62-48ACD4FFD384}" uniqueName="4" name="description" queryTableFieldId="4" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{EBBFCEC0-7D31-4CAD-A2DD-E444E8C840AD}" uniqueName="5" name="created" queryTableFieldId="5" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{235BBD11-52A4-432B-B259-1FEF7849A476}" uniqueName="6" name="prompt_cost_per_1m" queryTableFieldId="6" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{C125A326-71DC-498F-9CF6-9D4261986ABF}" uniqueName="7" name="completion_cost_per_1m" queryTableFieldId="7" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{C48D515D-EA76-4B8D-9D9B-3F86005C986D}" uniqueName="8" name="avg_cost_per_1m" queryTableFieldId="8" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{0C9AC00E-B68D-4AF7-9758-7543FA934B04}" uniqueName="9" name="request_cost" queryTableFieldId="9" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{CED2343B-816C-4F54-B994-E7FC118F7157}" uniqueName="10" name="image_cost" queryTableFieldId="10" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{6D67746F-12ED-4C55-AF34-2427D5CEA21F}" uniqueName="11" name="is_free" queryTableFieldId="11" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{D41C5152-EBB5-4D0D-A3D0-E2AF2584030A}" uniqueName="12" name="param_size" queryTableFieldId="12" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{3F7A75A1-5B17-4021-B0DF-2D6D58413453}" uniqueName="13" name="context_length" queryTableFieldId="13" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{77302B12-EFD5-4388-8BAA-BE5B0C3E0D4D}" uniqueName="14" name="architecture" queryTableFieldId="14" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{A4F53FD9-655C-485A-AF2A-687B004D91BB}" uniqueName="15" name="top_provider" queryTableFieldId="15" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{8DC3E8E9-B9CD-4A00-ABDC-CAEB3EF2F82E}" uniqueName="16" name="per_request_limits" queryTableFieldId="16" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{89C9A0EC-EEDE-4BF2-9AD6-BFB8C497DC96}" uniqueName="17" name="supported_parameters" queryTableFieldId="17" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{782F3ED8-5B9C-4F0A-9BF7-C9083C418B46}" uniqueName="18" name="default_parameters" queryTableFieldId="18" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{B52B03E2-D483-4B78-B500-90C21984E5CF}" uniqueName="19" name="last_updated" queryTableFieldId="19" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{A9E6322E-6414-4705-8C48-2E513F4761A1}" uniqueName="20" name="created_at" queryTableFieldId="20" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{78D3B969-8519-472B-B7DC-40B2AB389EDF}" uniqueName="1" name="model_id" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{2775870E-97E4-4A13-8631-08858414ABE9}" uniqueName="2" name="canonical_slug" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{9123C448-65CD-42A3-A8DF-FA33362CF2EB}" uniqueName="3" name="model_name" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{23ACEE67-B62B-4941-8C62-48ACD4FFD384}" uniqueName="4" name="description" queryTableFieldId="4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{EBBFCEC0-7D31-4CAD-A2DD-E444E8C840AD}" uniqueName="5" name="created" queryTableFieldId="5" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{235BBD11-52A4-432B-B259-1FEF7849A476}" uniqueName="6" name="prompt_cost_per_1m" queryTableFieldId="6" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{C125A326-71DC-498F-9CF6-9D4261986ABF}" uniqueName="7" name="completion_cost_per_1m" queryTableFieldId="7" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{C48D515D-EA76-4B8D-9D9B-3F86005C986D}" uniqueName="8" name="avg_cost_per_1m" queryTableFieldId="8" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{0C9AC00E-B68D-4AF7-9758-7543FA934B04}" uniqueName="9" name="request_cost" queryTableFieldId="9" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{CED2343B-816C-4F54-B994-E7FC118F7157}" uniqueName="10" name="image_cost" queryTableFieldId="10" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{6D67746F-12ED-4C55-AF34-2427D5CEA21F}" uniqueName="11" name="is_free" queryTableFieldId="11" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{D41C5152-EBB5-4D0D-A3D0-E2AF2584030A}" uniqueName="12" name="param_size" queryTableFieldId="12" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{3F7A75A1-5B17-4021-B0DF-2D6D58413453}" uniqueName="13" name="context_length" queryTableFieldId="13" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{77302B12-EFD5-4388-8BAA-BE5B0C3E0D4D}" uniqueName="14" name="architecture" queryTableFieldId="14" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{A4F53FD9-655C-485A-AF2A-687B004D91BB}" uniqueName="15" name="top_provider" queryTableFieldId="15" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{8DC3E8E9-B9CD-4A00-ABDC-CAEB3EF2F82E}" uniqueName="16" name="per_request_limits" queryTableFieldId="16" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{89C9A0EC-EEDE-4BF2-9AD6-BFB8C497DC96}" uniqueName="17" name="supported_parameters" queryTableFieldId="17" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{782F3ED8-5B9C-4F0A-9BF7-C9083C418B46}" uniqueName="18" name="default_parameters" queryTableFieldId="18" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{B52B03E2-D483-4B78-B500-90C21984E5CF}" uniqueName="19" name="last_updated" queryTableFieldId="19" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{A9E6322E-6414-4705-8C48-2E513F4761A1}" uniqueName="20" name="created_at" queryTableFieldId="20" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1414,7 +1414,7 @@
       <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="1" t="s">
         <v>164</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1546,7 +1546,9 @@
         <v>126</v>
       </c>
       <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
+      <c r="O4" s="11" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
@@ -1793,7 +1795,6 @@
       <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L10" s="13"/>
       <c r="M10" s="1" t="s">
         <v>141</v>
       </c>
@@ -1829,7 +1830,7 @@
       <c r="J11" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="1" t="s">
         <v>176</v>
       </c>
       <c r="M11" s="1" t="s">
@@ -1869,7 +1870,9 @@
         <v>127</v>
       </c>
       <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="O12" s="11" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -1899,7 +1902,6 @@
       <c r="I13" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L13" s="13"/>
       <c r="M13" s="1" t="s">
         <v>125</v>
       </c>

--- a/artifacts/tables/model-analysis.xlsx
+++ b/artifacts/tables/model-analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jn\dev\llm-ensemble\artifacts\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF1B7F5-8C71-43B7-A2D3-19626EF5B045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91696B4B-7FF1-492D-A209-D1AE84EACF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D1A87F95-65CE-44FE-B65A-B20AE0988E6A}"/>
   </bookViews>
